--- a/data/export/2026-10-16-operations.xlsx
+++ b/data/export/2026-10-16-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -991,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1068,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1222,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1583,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2506,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2519,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2567,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2586,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2622,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,41 +2650,37 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2652,7 +2688,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2676,17 +2712,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2696,45 +2732,41 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2772,7 +2804,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2888,7 +2920,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2970,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3031,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3050,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3086,3719 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72381D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-operations.xlsx
+++ b/data/export/2026-10-16-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1139,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1686,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,17 +1812,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1796,13 +1832,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2194,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2310,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2425,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2443,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2510,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2540,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2567,12 +2611,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2630,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2655,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2683,12 +2731,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2750,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2775,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2851,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2870,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2906,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2967,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2986,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +3011,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3087,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,18 +3251,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3215,52 +3279,56 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3268,7 +3336,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3350,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3292,17 +3360,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3312,13 +3380,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3331,60 +3403,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3474,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3408,33 +3484,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3447,60 +3527,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3598,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3524,17 +3608,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3544,13 +3628,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3563,22 +3651,22 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3611,12 +3699,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3718,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3666,7 +3754,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3767,32 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3727,12 +3815,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3740,13 +3828,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr"/>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3782,7 +3886,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3795,22 +3899,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3843,12 +3947,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3966,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3898,7 +4002,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3911,22 +4015,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3959,12 +4063,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3978,7 +4082,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4118,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4131,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4179,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4198,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4234,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4247,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4153,7 +4257,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4191,12 +4295,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4314,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4350,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4363,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A72381D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4269,7 +4373,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4307,12 +4411,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4430,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4466,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4479,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A92076D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4385,7 +4489,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4423,12 +4527,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4546,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4582,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4491,22 +4595,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4539,12 +4643,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4662,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4698,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4607,22 +4711,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4655,12 +4759,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4778,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,7 +4814,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4723,22 +4827,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4875,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4894,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4826,35 +4930,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +4991,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +5010,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4931,7 +5035,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4942,35 +5046,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A72381D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5107,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5126,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5162,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A92076D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5223,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5242,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5278,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5339,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5358,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5394,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5455,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5474,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5510,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5571,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5590,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5626,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5687,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5706,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5742,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57091D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5803,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5822,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5858,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5919,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5938,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5974,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6035,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6054,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6090,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A69930D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6052,7 +6156,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6170,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6206,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6267,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6286,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6322,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6383,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6402,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6438,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6499,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6518,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6554,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6516,7 +6620,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6634,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6555,18 +6659,22 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6687,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6589,7 +6697,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6599,40 +6707,44 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6646,7 +6758,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6656,33 +6768,37 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6695,52 +6811,56 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:05</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6748,7 +6868,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6762,43 +6882,2631 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>08:05</t>
         </is>
       </c>
-      <c r="W54" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X54" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y54" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z54" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC54" s="2" t="inlineStr"/>
-      <c r="AD54" s="2" t="inlineStr">
-        <is>
-          <t>—/16</t>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-operations.xlsx
+++ b/data/export/2026-10-16-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD76"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1397,24 +1397,24 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3273,70 +3273,66 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3350,7 +3346,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3360,107 +3356,103 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3474,7 +3466,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3484,17 +3476,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3504,17 +3496,13 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3515,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3537,7 +3525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3557,12 +3545,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -3584,7 +3572,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3598,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3623,22 +3611,22 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3639,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3661,7 +3649,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3671,32 +3659,36 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3704,7 +3696,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3718,7 +3710,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3728,33 +3720,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3763,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3777,7 +3773,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3787,32 +3783,36 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3828,29 +3828,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>物理seq28（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3860,17 +3844,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3880,13 +3864,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3899,60 +3887,64 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3966,7 +3958,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3976,33 +3968,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4015,32 +4011,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4068,7 +4064,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4076,13 +4072,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4131,7 +4143,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4141,7 +4153,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4179,12 +4191,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4198,7 +4210,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4247,7 +4259,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4257,7 +4269,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4295,12 +4307,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4314,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4363,7 +4375,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4373,7 +4385,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4411,12 +4423,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4430,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4479,7 +4491,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4489,7 +4501,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4527,12 +4539,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4546,7 +4558,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4595,22 +4607,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4643,12 +4655,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4662,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4711,22 +4723,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4759,12 +4771,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4778,7 +4790,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4827,7 +4839,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4837,7 +4849,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4875,12 +4887,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4894,7 +4906,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4943,22 +4955,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4991,12 +5003,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5010,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5059,22 +5071,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A72381D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5112,7 +5124,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5126,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5175,7 +5187,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A92076D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5185,7 +5197,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5223,12 +5235,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5242,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5291,7 +5303,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A72381D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5301,7 +5313,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5339,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5358,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5407,7 +5419,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A92076D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5417,7 +5429,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5455,7 +5467,7 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5523,7 +5535,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5533,7 +5545,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5571,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5590,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5639,7 +5651,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5649,7 +5661,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5687,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5706,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5755,22 +5767,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A57091D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5803,12 +5815,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5822,7 +5834,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5871,22 +5883,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5919,12 +5931,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5938,7 +5950,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5987,22 +5999,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A57091D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6040,7 +6052,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6054,7 +6066,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6103,22 +6115,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A69930D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6151,12 +6163,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6170,7 +6182,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6219,7 +6231,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6229,7 +6241,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6272,7 +6284,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6286,7 +6298,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6335,7 +6347,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62773D</t>
+          <t>沪A69930D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6345,7 +6357,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6383,12 +6395,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6402,7 +6414,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6451,22 +6463,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6499,12 +6511,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6518,7 +6530,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6567,22 +6579,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6620,7 +6632,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6634,7 +6646,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6659,92 +6671,84 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6758,7 +6762,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6768,99 +6772,91 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6868,7 +6864,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6882,7 +6878,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6892,17 +6888,17 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6917,82 +6913,78 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7006,7 +6998,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7016,17 +7008,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7041,40 +7033,40 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7112,7 +7104,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7126,7 +7118,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7156,13 +7148,17 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7175,7 +7171,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7185,7 +7181,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7195,40 +7191,44 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7242,7 +7242,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7252,33 +7252,37 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7291,24 +7295,24 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7321,34 +7325,34 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7362,7 +7366,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7397,12 +7401,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7415,52 +7419,56 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7468,7 +7476,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7482,7 +7490,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7492,33 +7500,37 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7531,22 +7543,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7579,12 +7591,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7598,7 +7610,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7647,7 +7659,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7657,7 +7669,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7695,7 +7707,7 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7714,7 +7726,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7763,7 +7775,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7773,7 +7785,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7783,40 +7795,44 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7830,7 +7846,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7840,33 +7856,37 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7899,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7889,7 +7909,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7927,12 +7947,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7946,7 +7966,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7995,60 +8015,64 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8062,7 +8086,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8072,33 +8096,37 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8111,22 +8139,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:32</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8164,7 +8192,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8178,7 +8206,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8227,22 +8255,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8275,12 +8303,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8294,7 +8322,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8319,7 +8347,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8343,22 +8371,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:48</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8391,12 +8419,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8410,7 +8438,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8459,7 +8487,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8469,7 +8497,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8507,12 +8535,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8526,7 +8554,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8575,7 +8603,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8585,7 +8613,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8623,12 +8651,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8642,7 +8670,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8667,22 +8695,18 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8719,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8705,7 +8729,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8743,12 +8767,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8762,7 +8786,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8811,22 +8835,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8859,12 +8883,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8878,7 +8902,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8903,22 +8927,18 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8931,22 +8951,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8979,12 +8999,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8998,7 +9018,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9023,22 +9043,18 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9067,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9061,7 +9077,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9104,7 +9120,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9118,7 +9134,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9148,13 +9164,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9187,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9177,7 +9197,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9215,12 +9235,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9234,7 +9254,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9259,22 +9279,18 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9287,22 +9303,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9335,12 +9351,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9354,7 +9370,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9379,18 +9395,22 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9403,22 +9423,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9451,12 +9471,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9470,41 +9490,633 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="W76" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X76" s="2" t="inlineStr">
+      <c r="X80" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y76" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z76" s="2" t="inlineStr">
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC76" s="2" t="inlineStr"/>
-      <c r="AD76" s="2" t="inlineStr">
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-16-operations.xlsx
+++ b/data/export/2026-10-16-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AD103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1991,32 +1991,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2024,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,37 +2052,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2183,7 +2187,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2260,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2299,7 +2303,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2343,32 +2347,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2376,7 +2384,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2400,37 +2408,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2504,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2616,7 +2624,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2670,7 +2678,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2744,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2775,7 +2783,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2790,7 +2798,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2864,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +2980,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3026,7 +3034,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3100,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3212,7 +3220,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3332,7 +3340,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,7 +3460,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3509,70 +3517,66 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3586,7 +3590,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3596,17 +3600,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3616,87 +3620,79 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3710,7 +3706,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3720,107 +3716,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3826,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3844,107 +3836,99 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3958,7 +3942,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3968,17 +3952,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3988,55 +3972,51 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4059,12 +4039,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4072,29 +4052,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq28（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4119,46 +4083,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4191,12 +4159,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4210,7 +4178,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4235,18 +4203,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4259,52 +4231,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4312,7 +4288,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4302,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4336,33 +4312,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4375,60 +4355,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4442,7 +4426,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4452,33 +4436,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4491,60 +4479,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4558,7 +4550,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4568,33 +4560,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4607,60 +4603,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4684,33 +4684,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4723,32 +4727,32 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4771,12 +4775,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4784,13 +4788,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4815,7 +4835,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4839,60 +4859,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4906,7 +4930,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4916,33 +4940,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4955,60 +4983,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5022,7 +5054,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5032,33 +5064,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5071,60 +5107,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5138,7 +5178,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5148,33 +5188,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5231,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5197,7 +5241,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5207,40 +5251,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5254,7 +5302,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5264,33 +5312,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5355,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A72381D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5313,7 +5365,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5351,12 +5403,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5370,7 +5422,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5395,7 +5447,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5419,7 +5471,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A92076D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5429,7 +5481,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5467,12 +5519,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5486,7 +5538,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5535,32 +5587,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5583,12 +5635,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5596,13 +5648,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5651,22 +5719,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5699,12 +5767,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5718,7 +5786,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5767,22 +5835,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5815,12 +5883,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5834,7 +5902,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5883,7 +5951,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5893,7 +5961,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5903,12 +5971,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5931,12 +5999,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5944,13 +6012,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5999,22 +6083,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A57091D</t>
+          <t>沪A72381D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6047,12 +6131,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6066,7 +6150,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6115,22 +6199,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A92076D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6163,12 +6247,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6182,7 +6266,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6231,7 +6315,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6241,7 +6325,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6279,12 +6363,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6298,7 +6382,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6347,7 +6431,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A69930D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6357,7 +6441,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6395,12 +6479,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6414,7 +6498,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6463,7 +6547,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6473,7 +6557,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6511,12 +6595,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6530,7 +6614,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6579,7 +6663,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A62773D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6589,7 +6673,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6627,12 +6711,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6646,7 +6730,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6695,7 +6779,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A57091D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6705,7 +6789,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6743,12 +6827,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6762,7 +6846,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6811,7 +6895,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6821,7 +6905,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6859,12 +6943,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6878,7 +6962,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6903,22 +6987,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6931,22 +7011,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6984,7 +7064,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6998,7 +7078,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7023,22 +7103,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7051,22 +7127,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A69930D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7099,12 +7175,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7118,7 +7194,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7143,84 +7219,76 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7228,7 +7296,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7242,7 +7310,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7252,99 +7320,91 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7352,7 +7412,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7366,7 +7426,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7376,107 +7436,99 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7490,7 +7542,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7500,65 +7552,61 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7596,7 +7644,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7610,7 +7658,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7640,41 +7688,45 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7707,12 +7759,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7726,7 +7778,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7751,88 +7803,88 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7846,7 +7898,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7856,17 +7908,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7881,40 +7933,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7947,12 +7999,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7966,7 +8018,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7991,88 +8043,88 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8086,7 +8138,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8096,17 +8148,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8116,45 +8168,41 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8187,12 +8235,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8206,7 +8254,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8231,46 +8279,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8303,12 +8355,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8322,7 +8374,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8352,41 +8404,45 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8419,12 +8475,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8438,7 +8494,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8463,46 +8519,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8535,12 +8595,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8554,7 +8614,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8579,46 +8639,50 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8651,12 +8715,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8670,7 +8734,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8695,7 +8759,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8706,7 +8770,7 @@
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8783,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8729,7 +8793,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8739,40 +8803,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8786,7 +8854,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8796,33 +8864,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8835,52 +8907,56 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:48</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8888,7 +8964,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8902,7 +8978,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8912,33 +8988,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8951,60 +9031,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9018,7 +9102,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9028,33 +9112,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9067,22 +9155,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:05</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9120,7 +9208,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9134,7 +9222,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9164,17 +9252,13 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9271,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9197,7 +9281,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9207,32 +9291,36 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9240,7 +9328,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9254,7 +9342,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9264,33 +9352,37 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9303,52 +9395,56 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9356,7 +9452,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9370,7 +9466,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9380,17 +9476,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9405,12 +9501,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9423,22 +9519,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9471,12 +9567,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9490,7 +9586,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9520,17 +9616,13 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9635,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9553,7 +9645,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9563,40 +9655,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9610,7 +9706,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9620,17 +9716,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9640,13 +9736,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9759,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9669,7 +9769,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9707,12 +9807,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9726,7 +9826,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9756,17 +9856,13 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9875,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9789,7 +9885,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9799,40 +9895,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9846,7 +9946,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9856,33 +9956,37 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9999,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9905,7 +10009,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9943,12 +10047,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9962,7 +10066,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9992,17 +10096,13 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10115,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10025,7 +10125,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10035,40 +10135,44 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10082,43 +10186,2675 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="W81" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X81" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y81" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z81" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB81" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC81" s="2" t="inlineStr"/>
-      <c r="AD81" s="2" t="inlineStr">
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-operations.xlsx
+++ b/data/export/2026-10-16-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3928,17 +3928,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4796,17 +4796,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5416,17 +5416,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6404,17 +6404,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7268,17 +7268,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7888,12 +7888,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8136,17 +8136,17 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8256,17 +8256,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8752,17 +8752,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9488,17 +9488,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10232,17 +10232,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10352,17 +10352,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10968,12 +10968,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11340,17 +11340,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11507,32 +11507,36 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11540,7 +11544,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11564,17 +11568,17 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11584,17 +11588,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11637,19 +11641,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11664,7 +11668,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11713,12 +11717,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11751,32 +11755,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11784,7 +11792,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11808,17 +11816,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11828,12 +11836,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11871,32 +11879,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11904,7 +11916,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11928,17 +11940,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11948,17 +11960,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11991,32 +12003,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12024,7 +12040,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12048,17 +12064,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12068,12 +12084,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12111,32 +12127,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12144,7 +12164,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12168,17 +12188,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12188,17 +12208,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12284,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12313,12 +12333,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12404,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12428,17 +12448,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -12508,7 +12528,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12552,17 +12572,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12706,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12830,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12954,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13156,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13190,7 +13210,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -13260,7 +13280,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13314,7 +13334,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -13438,7 +13458,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -13562,7 +13582,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13652,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13686,7 +13706,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13776,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13800,12 +13820,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
@@ -14070,7 +14090,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -14140,7 +14160,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14184,12 +14204,12 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
@@ -14260,7 +14280,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14330,7 +14350,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -14396,7 +14416,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14450,7 +14470,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -14520,7 +14540,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14564,17 +14584,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14714,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -14814,7 +14834,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -14880,7 +14900,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14934,7 +14954,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15024,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15058,7 +15078,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -15128,7 +15148,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15177,12 +15197,12 @@
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15322,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15504,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15538,7 +15558,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15678,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -15844,7 +15864,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15898,7 +15918,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -16022,7 +16042,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -16088,7 +16108,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16132,17 +16152,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -16262,7 +16282,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16406,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -16588,7 +16608,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16642,7 +16662,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -16712,7 +16732,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16766,7 +16786,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16906,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -17010,7 +17030,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -17080,7 +17100,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17134,7 +17154,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -17200,7 +17220,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17244,12 +17264,12 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
@@ -17320,7 +17340,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17364,12 +17384,12 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
@@ -17498,7 +17518,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17588,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17612,17 +17632,17 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -17692,7 +17712,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17746,7 +17766,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -17870,7 +17890,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -17994,7 +18014,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -18064,7 +18084,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18118,7 +18138,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -18188,7 +18208,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18242,7 +18262,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -18366,7 +18386,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -18436,7 +18456,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18490,7 +18510,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18634,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18704,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18738,7 +18758,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -18862,7 +18882,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -18986,7 +19006,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -19110,7 +19130,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19254,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -19300,7 +19320,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19614,7 +19634,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19704,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19738,7 +19758,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -19862,7 +19882,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19952,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -19976,17 +19996,17 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -20110,7 +20130,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -20180,7 +20200,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20234,7 +20254,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -20358,7 +20378,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -20482,7 +20502,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -20606,7 +20626,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20750,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20874,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -20924,7 +20944,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20978,7 +20998,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -21172,7 +21192,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21216,12 +21236,12 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
@@ -21424,7 +21444,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21544,7 +21564,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21593,12 +21613,12 @@
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -21668,7 +21688,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21722,7 +21742,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -21792,7 +21812,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21836,12 +21856,12 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
@@ -21916,7 +21936,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21960,17 +21980,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22060,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22094,7 +22114,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -22164,7 +22184,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22218,7 +22238,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -22288,7 +22308,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22342,7 +22362,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -22466,7 +22486,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -22536,7 +22556,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22590,7 +22610,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22734,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -22838,7 +22858,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22982,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23052,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23086,7 +23106,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -23210,7 +23230,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -23334,7 +23354,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -23404,7 +23424,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23458,7 +23478,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -23582,7 +23602,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -23768,7 +23788,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23822,7 +23842,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -23865,12 +23885,12 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
@@ -23892,7 +23912,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23941,12 +23961,12 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -23979,32 +23999,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>18:01</t>
@@ -24012,7 +24036,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24036,17 +24060,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24056,13 +24080,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC191" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC191" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -24095,32 +24123,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -24128,7 +24160,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24152,17 +24184,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24172,17 +24204,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24252,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq29推进至seq35，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -24248,7 +24280,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24318,7 +24350,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -24351,32 +24383,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24384,7 +24420,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24408,17 +24444,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24428,17 +24464,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -24471,32 +24507,36 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -24504,7 +24544,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24528,17 +24568,17 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA195" s="2" t="inlineStr">
@@ -24548,12 +24588,12 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
@@ -24591,12 +24631,12 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -24624,7 +24664,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24632,10 +24672,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R196" s="2" t="inlineStr"/>
-      <c r="S196" s="2" t="inlineStr"/>
-      <c r="T196" s="2" t="inlineStr"/>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V196" s="2" t="inlineStr">
         <is>
           <t>19:20</t>
@@ -24678,7 +24734,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -24744,7 +24800,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24798,7 +24854,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -24864,7 +24920,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24918,7 +24974,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -24951,32 +25007,36 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -24984,7 +25044,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25008,17 +25068,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -25028,12 +25088,12 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
@@ -25104,7 +25164,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25158,7 +25218,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -25224,7 +25284,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25278,7 +25338,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -25344,7 +25404,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25398,7 +25458,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -25464,7 +25524,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25518,7 +25578,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -25588,7 +25648,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25632,12 +25692,12 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -26080,7 +26140,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26124,12 +26184,12 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
@@ -26204,7 +26264,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26253,12 +26313,12 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26568,7 +26628,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26617,7 +26677,7 @@
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
@@ -26692,7 +26752,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26736,12 +26796,12 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
@@ -27114,7 +27174,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -27238,7 +27298,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27556,7 +27616,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27600,12 +27660,12 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
@@ -27680,7 +27740,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27724,17 +27784,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28168,7 +28228,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28217,12 +28277,12 @@
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28596,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28580,12 +28640,12 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
@@ -28784,7 +28844,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28828,12 +28888,12 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
@@ -28908,7 +28968,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28957,7 +29017,7 @@
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
@@ -29086,7 +29146,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -29524,7 +29584,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29568,17 +29628,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30076,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30077,12 +30137,12 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30396,7 +30456,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30452,12 +30512,12 @@
       </c>
       <c r="AB243" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
@@ -30586,7 +30646,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31702,7 +31762,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32640,7 +32700,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32684,12 +32744,12 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
@@ -32942,7 +33002,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33132,7 +33192,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33176,12 +33236,12 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
@@ -33310,7 +33370,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33504,7 +33564,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33553,7 +33613,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33876,7 +33936,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33925,12 +33985,12 @@
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34000,7 +34060,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34044,17 +34104,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34368,7 +34428,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34412,12 +34472,12 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34736,7 +34796,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34780,12 +34840,12 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
@@ -35038,7 +35098,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35162,7 +35222,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35356,7 +35416,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35400,12 +35460,12 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
@@ -35604,7 +35664,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35653,7 +35713,7 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35972,7 +36032,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36016,17 +36076,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36096,7 +36156,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36145,12 +36205,12 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -36584,7 +36644,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36628,12 +36688,12 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
@@ -36762,7 +36822,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36956,7 +37016,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37000,12 +37060,12 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
@@ -37130,7 +37190,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37444,7 +37504,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37488,12 +37548,12 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
@@ -37541,24 +37601,24 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -37568,7 +37628,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37617,12 +37677,12 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37665,24 +37725,24 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37692,7 +37752,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37741,7 +37801,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37779,32 +37839,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37812,7 +37876,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37836,17 +37900,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37856,12 +37920,12 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
@@ -37899,32 +37963,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37932,7 +38000,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37956,17 +38024,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37976,17 +38044,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -38019,32 +38087,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -38052,7 +38124,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38076,17 +38148,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38096,12 +38168,12 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
@@ -38139,32 +38211,36 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -38172,7 +38248,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38196,17 +38272,17 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA306" s="2" t="inlineStr">
@@ -38216,12 +38292,12 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
@@ -38292,7 +38368,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38341,7 +38417,7 @@
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
@@ -38412,7 +38488,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38456,17 +38532,17 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-operations.xlsx
+++ b/data/export/2026-10-16-operations.xlsx
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3928,17 +3928,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5168,17 +5168,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5416,17 +5416,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6404,17 +6404,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8752,17 +8752,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10108,17 +10108,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10232,17 +10232,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10734,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11712,17 +11712,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11960,17 +11960,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12137,12 +12137,12 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -12251,32 +12251,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12284,7 +12288,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12308,17 +12312,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12328,17 +12332,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -12371,32 +12375,36 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -12404,7 +12412,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12428,17 +12436,17 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -12448,17 +12456,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12714,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12838,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12962,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13164,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13200,17 +13208,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13660,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13696,17 +13704,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14168,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14209,12 +14217,12 @@
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14424,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14594,7 +14602,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14908,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15024,7 +15032,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15068,17 +15076,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15210,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16050,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -16282,7 +16290,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -16406,7 +16414,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -16732,7 +16740,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16776,17 +16784,17 @@
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -17100,7 +17108,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17144,17 +17152,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -17340,7 +17348,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17389,12 +17397,12 @@
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17650,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -17712,7 +17720,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -18084,7 +18092,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18208,7 +18216,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18252,17 +18260,17 @@
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -18882,7 +18890,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -19006,7 +19014,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -19758,7 +19766,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20014,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -20200,7 +20208,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20244,17 +20252,17 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -20626,7 +20634,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -20750,7 +20758,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -21618,7 +21626,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -21742,7 +21750,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -21812,7 +21820,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21861,12 +21869,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22316,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22352,17 +22360,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -22486,7 +22494,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -22556,7 +22564,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22600,17 +22608,17 @@
       </c>
       <c r="AB179" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -23052,7 +23060,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23354,7 +23362,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -23788,7 +23796,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23966,7 +23974,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24222,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -24854,7 +24862,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -24887,32 +24895,36 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -24920,7 +24932,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24944,17 +24956,17 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA198" s="2" t="inlineStr">
@@ -24964,17 +24976,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -25017,24 +25029,24 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O199" s="2" t="inlineStr">
@@ -25044,7 +25056,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25093,12 +25105,12 @@
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -25131,32 +25143,36 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -25164,7 +25180,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25188,17 +25204,17 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA200" s="2" t="inlineStr">
@@ -25208,17 +25224,17 @@
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -25251,32 +25267,36 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -25284,7 +25304,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25308,17 +25328,17 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA201" s="2" t="inlineStr">
@@ -25328,17 +25348,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25424,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25524,7 +25544,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25648,7 +25668,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -26140,7 +26160,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26628,7 +26648,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -27616,7 +27636,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27740,7 +27760,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -28596,7 +28616,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28968,7 +28988,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29584,7 +29604,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -32700,7 +32720,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -33192,7 +33212,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33564,7 +33584,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -34060,7 +34080,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34796,7 +34816,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -35416,7 +35436,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35664,7 +35684,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -36032,7 +36052,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -37016,7 +37036,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37504,7 +37524,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37752,7 +37772,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -38000,7 +38020,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38124,7 +38144,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38248,7 +38268,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38368,7 +38388,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38488,7 +38508,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
